--- a/0. Gráficos finales/0. Gráficas FINALES.xlsx
+++ b/0. Gráficos finales/0. Gráficas FINALES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Desktop\TFM\0_official_repository\bias_audit_LLM\0. Gráficos finales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528A2779-4363-4E18-B59E-F44C07B7D3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6CA411-3CD5-4472-8472-D50EF443D13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E_Llama_vs_FinGPT" sheetId="1" r:id="rId1"/>
@@ -1865,7 +1865,7 @@
                   <a:srgbClr val="44546A"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Llama (Environment -  E) - </a:t>
+              <a:t>Llama - </a:t>
             </a:r>
             <a:r>
               <a:rPr lang="es-ES"/>
@@ -2290,7 +2290,7 @@
                   <a:srgbClr val="44546A"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Llama (Environment -  E) - </a:t>
+              <a:t>Llama - </a:t>
             </a:r>
             <a:r>
               <a:rPr lang="es-ES"/>
@@ -4389,7 +4389,7 @@
                   <a:srgbClr val="44546A"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>FinGPT (Environment -  E) - Number of discrepancies by Bias using vs. not using Vigeo Eiris in Environment audit</a:t>
+              <a:t>FinGPT - Number of discrepancies by Bias using vs. not using Vigeo Eiris in Environment audit</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -5212,7 +5212,7 @@
                   <a:srgbClr val="44546A"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>FinGPT (Environment -  E) - Deviation by Bias using vs. not using Vigeo Eiris in Environment audit</a:t>
+              <a:t>FinGPT - Deviation by Bias using vs. not using Vigeo Eiris in Environment audit</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -7304,8 +7304,17 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-ES"/>
-              <a:t>Number of discrepancies by Bias without using Vigeo Eiris</a:t>
+              <a:t>Number of discrepancies by Bias without using Vigeo Eiris - </a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="es-ES" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>(Environment -  E) </a:t>
+            </a:r>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -7713,8 +7722,17 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-ES"/>
-              <a:t>Deviation by Bias without using Vigeo Eiris</a:t>
+              <a:t>Deviation by Bias without using Vigeo Eiris - </a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="es-ES" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>(Environment -  E) </a:t>
+            </a:r>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -8127,7 +8145,7 @@
                   <a:srgbClr val="44546A"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Comparison of Discrepancies without using Vigeo Eiris in Social audits</a:t>
+              <a:t>Comparison of Discrepancies without using Vigeo Eiris in Social audits - (Social - S)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8540,7 +8558,7 @@
                   <a:srgbClr val="44546A"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Comparison of Deviation without using Vigeo Eiris in Social audits</a:t>
+              <a:t>Comparison of Deviation without using Vigeo Eiris in Social audits - (Social - S)</a:t>
             </a:r>
           </a:p>
         </c:rich>
